--- a/CSSP-Decommisioning-1708.xlsx
+++ b/CSSP-Decommisioning-1708.xlsx
@@ -5,17 +5,33 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raditya.nugraha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github-hop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ACB5E64A-E324-494C-9331-9C3A5881412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8927FC80-FE98-400E-9B82-1F53D1E4ECF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E0F66C2E-BA15-40C6-82D8-BB5EAF94E7F8}"/>
   </bookViews>
   <sheets>
     <sheet name="cssp-administration (4)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'cssp-administration (4)'!$A$1:$AO$369</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -16209,6 +16225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E4DA5C-5563-4366-9E43-4512C5748AE7}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AO369"/>
   <sheetFormatPr defaultColWidth="35" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16378,7 +16395,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -16471,7 +16488,7 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
     </row>
-    <row r="3" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -16568,7 +16585,7 @@
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
     </row>
-    <row r="4" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>79</v>
       </c>
@@ -16657,7 +16674,7 @@
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
     </row>
-    <row r="5" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>94</v>
       </c>
@@ -16756,7 +16773,7 @@
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
     </row>
-    <row r="6" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>109</v>
       </c>
@@ -16853,7 +16870,7 @@
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
     </row>
-    <row r="7" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>124</v>
       </c>
@@ -16948,7 +16965,7 @@
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
     </row>
-    <row r="8" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>137</v>
       </c>
@@ -17051,7 +17068,7 @@
       <c r="AN8" s="2"/>
       <c r="AO8" s="2"/>
     </row>
-    <row r="9" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
@@ -17158,7 +17175,7 @@
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
     </row>
-    <row r="10" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>176</v>
       </c>
@@ -17271,7 +17288,7 @@
       <c r="AN10" s="2"/>
       <c r="AO10" s="2"/>
     </row>
-    <row r="11" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>200</v>
       </c>
@@ -17380,7 +17397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>219</v>
       </c>
@@ -17477,7 +17494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>228</v>
       </c>
@@ -17596,7 +17613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>252</v>
       </c>
@@ -17713,7 +17730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>268</v>
       </c>
@@ -17824,7 +17841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>288</v>
       </c>
@@ -17921,7 +17938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>303</v>
       </c>
@@ -18032,7 +18049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>317</v>
       </c>
@@ -18127,7 +18144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>327</v>
       </c>
@@ -18240,7 +18257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>343</v>
       </c>
@@ -18361,7 +18378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="144" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" ht="144" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>363</v>
       </c>
@@ -18482,7 +18499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>382</v>
       </c>
@@ -18599,7 +18616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>402</v>
       </c>
@@ -18718,7 +18735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>424</v>
       </c>
@@ -18835,7 +18852,7 @@
       </c>
       <c r="AO24" s="2"/>
     </row>
-    <row r="25" spans="1:41" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:41" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>445</v>
       </c>
@@ -18952,7 +18969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="403.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>463</v>
       </c>
@@ -19069,7 +19086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>476</v>
       </c>
@@ -19188,7 +19205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>498</v>
       </c>
@@ -19305,7 +19322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>512</v>
       </c>
@@ -19428,7 +19445,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="30" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>534</v>
       </c>
@@ -19547,7 +19564,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:41" ht="244.8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:41" ht="244.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>555</v>
       </c>
@@ -19664,7 +19681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>577</v>
       </c>
@@ -19781,7 +19798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>591</v>
       </c>
@@ -19900,7 +19917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>611</v>
       </c>
@@ -20021,7 +20038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>630</v>
       </c>
@@ -20142,7 +20159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>649</v>
       </c>
@@ -20237,7 +20254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>656</v>
       </c>
@@ -20334,7 +20351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>669</v>
       </c>
@@ -20455,7 +20472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>690</v>
       </c>
@@ -20574,7 +20591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>705</v>
       </c>
@@ -20691,7 +20708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>724</v>
       </c>
@@ -20784,7 +20801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>737</v>
       </c>
@@ -20877,7 +20894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>744</v>
       </c>
@@ -20994,7 +21011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>759</v>
       </c>
@@ -21087,7 +21104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>772</v>
       </c>
@@ -21180,7 +21197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>782</v>
       </c>
@@ -21297,7 +21314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>796</v>
       </c>
@@ -21394,7 +21411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>801</v>
       </c>
@@ -21489,7 +21506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>807</v>
       </c>
@@ -21584,7 +21601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>813</v>
       </c>
@@ -21677,7 +21694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>818</v>
       </c>
@@ -21774,7 +21791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>827</v>
       </c>
@@ -21893,7 +21910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>840</v>
       </c>
@@ -21988,7 +22005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>845</v>
       </c>
@@ -22083,7 +22100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>851</v>
       </c>
@@ -22176,7 +22193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>856</v>
       </c>
@@ -22271,7 +22288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>861</v>
       </c>
@@ -22388,7 +22405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>872</v>
       </c>
@@ -22507,7 +22524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>885</v>
       </c>
@@ -22624,7 +22641,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>903</v>
       </c>
@@ -22733,7 +22750,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="61" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>918</v>
       </c>
@@ -22826,7 +22843,7 @@
       </c>
       <c r="AO61" s="2"/>
     </row>
-    <row r="62" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>928</v>
       </c>
@@ -22919,7 +22936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>935</v>
       </c>
@@ -23036,7 +23053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>949</v>
       </c>
@@ -23157,7 +23174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>969</v>
       </c>
@@ -23276,7 +23293,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="66" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>982</v>
       </c>
@@ -23395,7 +23412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>1001</v>
       </c>
@@ -23512,7 +23529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>1021</v>
       </c>
@@ -23611,7 +23628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>1029</v>
       </c>
@@ -23732,7 +23749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>1045</v>
       </c>
@@ -23835,7 +23852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>1058</v>
       </c>
@@ -23954,7 +23971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>1074</v>
       </c>
@@ -24073,7 +24090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>1090</v>
       </c>
@@ -24192,7 +24209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>1100</v>
       </c>
@@ -24313,7 +24330,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>1115</v>
       </c>
@@ -24432,7 +24449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>1136</v>
       </c>
@@ -24549,7 +24566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>1153</v>
       </c>
@@ -24666,7 +24683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:41" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:41" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>1172</v>
       </c>
@@ -24783,7 +24800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>1193</v>
       </c>
@@ -24902,7 +24919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>1216</v>
       </c>
@@ -24997,7 +25014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>1229</v>
       </c>
@@ -25116,7 +25133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>1247</v>
       </c>
@@ -25235,7 +25252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>1265</v>
       </c>
@@ -25354,7 +25371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>1281</v>
       </c>
@@ -25473,7 +25490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>1301</v>
       </c>
@@ -25592,7 +25609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>1316</v>
       </c>
@@ -25709,7 +25726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>1333</v>
       </c>
@@ -25826,7 +25843,7 @@
       </c>
       <c r="AO87" s="2"/>
     </row>
-    <row r="88" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>1354</v>
       </c>
@@ -25943,7 +25960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>1375</v>
       </c>
@@ -26038,7 +26055,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>1389</v>
       </c>
@@ -26155,7 +26172,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>1403</v>
       </c>
@@ -26272,7 +26289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>1420</v>
       </c>
@@ -26389,7 +26406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>1436</v>
       </c>
@@ -26506,7 +26523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>1455</v>
       </c>
@@ -26613,7 +26630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>1469</v>
       </c>
@@ -26734,7 +26751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>1488</v>
       </c>
@@ -26855,7 +26872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>1507</v>
       </c>
@@ -26972,7 +26989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>1523</v>
       </c>
@@ -27063,7 +27080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>1530</v>
       </c>
@@ -27180,7 +27197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>1544</v>
       </c>
@@ -27291,7 +27308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>1561</v>
       </c>
@@ -27402,7 +27419,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>1570</v>
       </c>
@@ -27523,7 +27540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>1584</v>
       </c>
@@ -27640,7 +27657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>1601</v>
       </c>
@@ -27757,7 +27774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>1618</v>
       </c>
@@ -27874,7 +27891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>1631</v>
       </c>
@@ -27991,7 +28008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>1648</v>
       </c>
@@ -28108,7 +28125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>1660</v>
       </c>
@@ -28211,7 +28228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>1675</v>
       </c>
@@ -28314,7 +28331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>1686</v>
       </c>
@@ -28431,7 +28448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>1706</v>
       </c>
@@ -28548,7 +28565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>1720</v>
       </c>
@@ -28665,7 +28682,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>1732</v>
       </c>
@@ -28758,7 +28775,7 @@
       </c>
       <c r="AO113" s="2"/>
     </row>
-    <row r="114" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>1746</v>
       </c>
@@ -28849,7 +28866,7 @@
       </c>
       <c r="AO114" s="2"/>
     </row>
-    <row r="115" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>1753</v>
       </c>
@@ -28948,7 +28965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>1768</v>
       </c>
@@ -29063,7 +29080,7 @@
       </c>
       <c r="AO116" s="2"/>
     </row>
-    <row r="117" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>1781</v>
       </c>
@@ -29180,7 +29197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>1798</v>
       </c>
@@ -29273,7 +29290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>1808</v>
       </c>
@@ -29390,7 +29407,7 @@
         <v>-365</v>
       </c>
     </row>
-    <row r="120" spans="1:41" ht="187.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:41" ht="187.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>1826</v>
       </c>
@@ -29507,7 +29524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>1839</v>
       </c>
@@ -29624,7 +29641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>1854</v>
       </c>
@@ -29741,7 +29758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>1866</v>
       </c>
@@ -29858,7 +29875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>1880</v>
       </c>
@@ -29975,7 +29992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>1891</v>
       </c>
@@ -30094,7 +30111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>1905</v>
       </c>
@@ -30211,7 +30228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>1920</v>
       </c>
@@ -30330,7 +30347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>1931</v>
       </c>
@@ -30447,7 +30464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>1952</v>
       </c>
@@ -30564,7 +30581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>1970</v>
       </c>
@@ -30685,7 +30702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>1993</v>
       </c>
@@ -30802,7 +30819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>2010</v>
       </c>
@@ -30895,7 +30912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>2019</v>
       </c>
@@ -30992,7 +31009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>2026</v>
       </c>
@@ -31109,7 +31126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>2042</v>
       </c>
@@ -31230,7 +31247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>2061</v>
       </c>
@@ -31347,7 +31364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>2071</v>
       </c>
@@ -31440,7 +31457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>2081</v>
       </c>
@@ -31533,7 +31550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>2092</v>
       </c>
@@ -31650,7 +31667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>2106</v>
       </c>
@@ -31767,7 +31784,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="141" spans="1:41" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:41" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>2119</v>
       </c>
@@ -31886,7 +31903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>2139</v>
       </c>
@@ -32007,7 +32024,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>2154</v>
       </c>
@@ -32124,7 +32141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>2168</v>
       </c>
@@ -32245,7 +32262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>2186</v>
       </c>
@@ -32340,7 +32357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>2200</v>
       </c>
@@ -32435,7 +32452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>2209</v>
       </c>
@@ -32556,7 +32573,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="148" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>2231</v>
       </c>
@@ -32673,7 +32690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>2247</v>
       </c>
@@ -32792,7 +32809,7 @@
       </c>
       <c r="AO149" s="2"/>
     </row>
-    <row r="150" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>2267</v>
       </c>
@@ -32909,7 +32926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>2288</v>
       </c>
@@ -33026,7 +33043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:41" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:41" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>2304</v>
       </c>
@@ -33143,7 +33160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>2323</v>
       </c>
@@ -33260,7 +33277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>2339</v>
       </c>
@@ -33355,7 +33372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>2346</v>
       </c>
@@ -33476,7 +33493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>2365</v>
       </c>
@@ -33571,7 +33588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>2375</v>
       </c>
@@ -33688,7 +33705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>2391</v>
       </c>
@@ -33781,7 +33798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>2398</v>
       </c>
@@ -33898,7 +33915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>2409</v>
       </c>
@@ -34015,7 +34032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>2421</v>
       </c>
@@ -34132,7 +34149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>2435</v>
       </c>
@@ -34253,7 +34270,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="163" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>2454</v>
       </c>
@@ -34372,7 +34389,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="164" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>2475</v>
       </c>
@@ -34465,7 +34482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>2484</v>
       </c>
@@ -34582,7 +34599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>2495</v>
       </c>
@@ -34701,7 +34718,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:41" ht="259.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:41" ht="259.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>2509</v>
       </c>
@@ -34822,7 +34839,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="168" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>2529</v>
       </c>
@@ -34939,7 +34956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>2549</v>
       </c>
@@ -35056,7 +35073,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>2568</v>
       </c>
@@ -35149,7 +35166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>2576</v>
       </c>
@@ -35266,7 +35283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>2592</v>
       </c>
@@ -35359,7 +35376,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="173" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>2602</v>
       </c>
@@ -35450,7 +35467,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="174" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>2609</v>
       </c>
@@ -35557,7 +35574,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="175" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>2625</v>
       </c>
@@ -35652,7 +35669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>2637</v>
       </c>
@@ -35773,7 +35790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>2656</v>
       </c>
@@ -35866,7 +35883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>2662</v>
       </c>
@@ -35969,7 +35986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>2672</v>
       </c>
@@ -36086,7 +36103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>2685</v>
       </c>
@@ -36205,7 +36222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>2705</v>
       </c>
@@ -36322,7 +36339,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="182" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>2717</v>
       </c>
@@ -36415,7 +36432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>2729</v>
       </c>
@@ -36532,7 +36549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>2742</v>
       </c>
@@ -36653,7 +36670,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>2757</v>
       </c>
@@ -36770,7 +36787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>2772</v>
       </c>
@@ -36863,7 +36880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>2783</v>
       </c>
@@ -36956,7 +36973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>2791</v>
       </c>
@@ -37049,7 +37066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>2799</v>
       </c>
@@ -37142,7 +37159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>2806</v>
       </c>
@@ -37235,7 +37252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>2816</v>
       </c>
@@ -37354,7 +37371,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="192" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>2836</v>
       </c>
@@ -37447,7 +37464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>2844</v>
       </c>
@@ -37558,7 +37575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>2858</v>
       </c>
@@ -37675,7 +37692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>2869</v>
       </c>
@@ -37792,7 +37809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>2880</v>
       </c>
@@ -37909,7 +37926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>2895</v>
       </c>
@@ -38002,7 +38019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>2906</v>
       </c>
@@ -38119,7 +38136,7 @@
       </c>
       <c r="AO198" s="2"/>
     </row>
-    <row r="199" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>2920</v>
       </c>
@@ -38240,7 +38257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>2941</v>
       </c>
@@ -38335,7 +38352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>2953</v>
       </c>
@@ -38430,7 +38447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>2961</v>
       </c>
@@ -38549,7 +38566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>2980</v>
       </c>
@@ -38668,7 +38685,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>2998</v>
       </c>
@@ -38787,7 +38804,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>3013</v>
       </c>
@@ -38906,7 +38923,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>3032</v>
       </c>
@@ -39027,7 +39044,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="207" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>3051</v>
       </c>
@@ -39124,7 +39141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>3062</v>
       </c>
@@ -39247,7 +39264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>3077</v>
       </c>
@@ -39364,7 +39381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>3087</v>
       </c>
@@ -39481,7 +39498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>3098</v>
       </c>
@@ -39604,7 +39621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:41" ht="403.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:41" ht="403.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>3110</v>
       </c>
@@ -39723,7 +39740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>3131</v>
       </c>
@@ -39840,7 +39857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>3146</v>
       </c>
@@ -39957,7 +39974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>3158</v>
       </c>
@@ -40050,7 +40067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>3166</v>
       </c>
@@ -40167,7 +40184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>3181</v>
       </c>
@@ -40284,7 +40301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>3194</v>
       </c>
@@ -40377,7 +40394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>3202</v>
       </c>
@@ -40494,7 +40511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>3214</v>
       </c>
@@ -40593,7 +40610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>3231</v>
       </c>
@@ -40684,7 +40701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>3236</v>
       </c>
@@ -40777,7 +40794,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="223" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>3246</v>
       </c>
@@ -40870,7 +40887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>3257</v>
       </c>
@@ -40969,7 +40986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>3268</v>
       </c>
@@ -41086,7 +41103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>3283</v>
       </c>
@@ -41185,7 +41202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>3291</v>
       </c>
@@ -41302,7 +41319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>3303</v>
       </c>
@@ -41397,7 +41414,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="229" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>3310</v>
       </c>
@@ -41502,7 +41519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:41" ht="172.8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:41" ht="172.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>3323</v>
       </c>
@@ -41605,7 +41622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>3337</v>
       </c>
@@ -41700,7 +41717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>3348</v>
       </c>
@@ -41803,7 +41820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>3359</v>
       </c>
@@ -41894,7 +41911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>3368</v>
       </c>
@@ -42011,7 +42028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>3382</v>
       </c>
@@ -42126,7 +42143,7 @@
       </c>
       <c r="AO235" s="2"/>
     </row>
-    <row r="236" spans="1:41" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:41" ht="158.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>3396</v>
       </c>
@@ -42219,7 +42236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:41" ht="201.6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:41" ht="201.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>3408</v>
       </c>
@@ -42338,7 +42355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>3426</v>
       </c>
@@ -42455,7 +42472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:41" ht="144" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:41" ht="144" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>3442</v>
       </c>
@@ -42570,7 +42587,7 @@
       </c>
       <c r="AO239" s="2"/>
     </row>
-    <row r="240" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>3457</v>
       </c>
@@ -42665,7 +42682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>3469</v>
       </c>
@@ -42760,7 +42777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:41" ht="316.8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:41" ht="316.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>3478</v>
       </c>
@@ -42855,7 +42872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="243" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>3489</v>
       </c>
@@ -43190,7 +43207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>3533</v>
       </c>
@@ -43404,7 +43421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>3557</v>
       </c>
@@ -43507,7 +43524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>3566</v>
       </c>
@@ -43600,7 +43617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>3572</v>
       </c>
@@ -43703,7 +43720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>3580</v>
       </c>
@@ -43800,7 +43817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>3594</v>
       </c>
@@ -43913,7 +43930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>3607</v>
       </c>
@@ -44006,7 +44023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>3619</v>
       </c>
@@ -44117,7 +44134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>3632</v>
       </c>
@@ -44210,7 +44227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>3639</v>
       </c>
@@ -44303,7 +44320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>3645</v>
       </c>
@@ -44400,7 +44417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>3651</v>
       </c>
@@ -44493,7 +44510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>3658</v>
       </c>
@@ -44598,7 +44615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>3667</v>
       </c>
@@ -44695,7 +44712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>3673</v>
       </c>
@@ -44806,7 +44823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>3682</v>
       </c>
@@ -44923,7 +44940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>3698</v>
       </c>
@@ -45034,7 +45051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>3709</v>
       </c>
@@ -45145,7 +45162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>3718</v>
       </c>
@@ -45262,7 +45279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>3731</v>
       </c>
@@ -45377,7 +45394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>3746</v>
       </c>
@@ -45474,7 +45491,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="268" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>3755</v>
       </c>
@@ -45597,7 +45614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:41" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:41" ht="409.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>3773</v>
       </c>
@@ -45698,7 +45715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:41" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:41" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>3789</v>
       </c>
@@ -45809,7 +45826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>3801</v>
       </c>
@@ -45908,7 +45925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>3815</v>
       </c>
@@ -46007,7 +46024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>3822</v>
       </c>
@@ -46118,7 +46135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>3836</v>
       </c>
@@ -46229,7 +46246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>3853</v>
       </c>
@@ -46348,7 +46365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>3869</v>
       </c>
@@ -46441,7 +46458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="277" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>3877</v>
       </c>
@@ -46534,7 +46551,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="278" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>3887</v>
       </c>
@@ -46647,7 +46664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>3903</v>
       </c>
@@ -46764,7 +46781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>3918</v>
       </c>
@@ -46881,7 +46898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>3932</v>
       </c>
@@ -46994,7 +47011,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="282" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>3947</v>
       </c>
@@ -47091,7 +47108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>3961</v>
       </c>
@@ -47198,7 +47215,7 @@
       </c>
       <c r="AO283" s="2"/>
     </row>
-    <row r="284" spans="1:41" ht="201.6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:41" ht="201.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>3977</v>
       </c>
@@ -47297,7 +47314,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="285" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>3991</v>
       </c>
@@ -47408,7 +47425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>4001</v>
       </c>
@@ -47503,7 +47520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>4013</v>
       </c>
@@ -47618,7 +47635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>4027</v>
       </c>
@@ -47715,7 +47732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>4038</v>
       </c>
@@ -47812,7 +47829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>4046</v>
       </c>
@@ -47933,7 +47950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>4058</v>
       </c>
@@ -48026,7 +48043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>4071</v>
       </c>
@@ -48137,7 +48154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>4084</v>
       </c>
@@ -48248,7 +48265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>4094</v>
       </c>
@@ -48365,7 +48382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>4109</v>
       </c>
@@ -48456,7 +48473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>4118</v>
       </c>
@@ -48551,7 +48568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>4131</v>
       </c>
@@ -48662,7 +48679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>4145</v>
       </c>
@@ -48759,7 +48776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>4156</v>
       </c>
@@ -48862,7 +48879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>4163</v>
       </c>
@@ -48973,7 +48990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>4174</v>
       </c>
@@ -49066,7 +49083,7 @@
       </c>
       <c r="AO301" s="2"/>
     </row>
-    <row r="302" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>4184</v>
       </c>
@@ -49169,7 +49186,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="303" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>4194</v>
       </c>
@@ -49280,7 +49297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="304" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>4205</v>
       </c>
@@ -49395,7 +49412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>4219</v>
       </c>
@@ -49508,7 +49525,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="306" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>4236</v>
       </c>
@@ -49619,7 +49636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>4250</v>
       </c>
@@ -49730,7 +49747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>4264</v>
       </c>
@@ -49837,7 +49854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>4278</v>
       </c>
@@ -49948,7 +49965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>4292</v>
       </c>
@@ -50059,7 +50076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>4306</v>
       </c>
@@ -50170,7 +50187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>4319</v>
       </c>
@@ -50281,7 +50298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>4328</v>
       </c>
@@ -50392,7 +50409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>4342</v>
       </c>
@@ -50503,7 +50520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>4352</v>
       </c>
@@ -50618,7 +50635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>4371</v>
       </c>
@@ -50725,7 +50742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>4383</v>
       </c>
@@ -50832,7 +50849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>4395</v>
       </c>
@@ -50943,7 +50960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>4408</v>
       </c>
@@ -51054,7 +51071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>4423</v>
       </c>
@@ -51165,7 +51182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>4433</v>
       </c>
@@ -51276,7 +51293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>4446</v>
       </c>
@@ -51387,7 +51404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>4456</v>
       </c>
@@ -51498,7 +51515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>4469</v>
       </c>
@@ -51609,7 +51626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>4483</v>
       </c>
@@ -51720,7 +51737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>4497</v>
       </c>
@@ -51831,7 +51848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>4510</v>
       </c>
@@ -51942,7 +51959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>4520</v>
       </c>
@@ -52049,7 +52066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>4531</v>
       </c>
@@ -52160,7 +52177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>4543</v>
       </c>
@@ -52263,7 +52280,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="331" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>4553</v>
       </c>
@@ -52358,7 +52375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>4560</v>
       </c>
@@ -52469,7 +52486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>4570</v>
       </c>
@@ -52580,7 +52597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>4579</v>
       </c>
@@ -52683,7 +52700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>4589</v>
       </c>
@@ -52794,7 +52811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>4599</v>
       </c>
@@ -52905,7 +52922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>4609</v>
       </c>
@@ -53016,7 +53033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>4621</v>
       </c>
@@ -53129,7 +53146,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="339" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>4637</v>
       </c>
@@ -53226,7 +53243,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="340" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>4650</v>
       </c>
@@ -53325,7 +53342,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="341" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>4658</v>
       </c>
@@ -53436,7 +53453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>4669</v>
       </c>
@@ -53547,7 +53564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>4680</v>
       </c>
@@ -53642,7 +53659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>4693</v>
       </c>
@@ -53735,7 +53752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>4702</v>
       </c>
@@ -53826,7 +53843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:41" ht="72" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:41" ht="72" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>4710</v>
       </c>
@@ -53919,7 +53936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:41" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:41" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>4717</v>
       </c>
@@ -54010,7 +54027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>4724</v>
       </c>
@@ -54103,7 +54120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>4731</v>
       </c>
@@ -54196,7 +54213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>4741</v>
       </c>
@@ -54287,7 +54304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>4746</v>
       </c>
@@ -54398,7 +54415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:41" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:41" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>4757</v>
       </c>
@@ -54509,7 +54526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>4768</v>
       </c>
@@ -54620,7 +54637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>4781</v>
       </c>
@@ -54717,7 +54734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>4794</v>
       </c>
@@ -54828,7 +54845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>4804</v>
       </c>
@@ -54921,7 +54938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>4809</v>
       </c>
@@ -55016,7 +55033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>4821</v>
       </c>
@@ -55109,7 +55126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>4833</v>
       </c>
@@ -55214,7 +55231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:41" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:41" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>4845</v>
       </c>
@@ -55311,7 +55328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>4858</v>
       </c>
@@ -55404,7 +55421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:41" ht="216" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:41" ht="216" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>4864</v>
       </c>
@@ -55495,7 +55512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>4873</v>
       </c>
@@ -55594,7 +55611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>4880</v>
       </c>
@@ -55697,7 +55714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:41" ht="302.39999999999998" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:41" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>4890</v>
       </c>
@@ -55792,7 +55809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:41" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:41" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>4901</v>
       </c>
@@ -55887,7 +55904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>4909</v>
       </c>
@@ -55992,7 +56009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:41" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:41" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>4927</v>
       </c>
@@ -56087,7 +56104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:41" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:41" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>4935</v>
       </c>
@@ -56183,6 +56200,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO369" xr:uid="{23E4DA5C-5563-4366-9E43-4512C5748AE7}">
+    <filterColumn colId="29">
+      <customFilters>
+        <customFilter val="2026-08-17*"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>